--- a/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -845,7 +845,7 @@
   </si>
   <si>
     <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).  
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration).  
 Period（期間）は時間の範囲を指定する。使用状況は、範囲全体が適用されるか（たとえば、「患者はこの時間範囲で入院していた」）、範囲から1つの値が適用されるか（たとえば、「この2回の間に患者に投与する」）を指定する。  
 Period（期間）は、Duration（時間区間＝経過時間の測定値）には使用されない。 [Duration]（datatypes.html＃Duration）を参照のこと。  
 This is not a duration - that's a measure of time (a separate type), but a duration that occurs at a fixed value of time. A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times"). If duration is required, specify the type as Interval|Duration.  

--- a/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="511">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -375,7 +375,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -526,7 +526,7 @@
     <t>健康保険における被保険者証番号の枝番を示す拡張</t>
   </si>
   <si>
-    <t>健康保険における被保険者証番号を示す拡張。2桁の全角数字文字列。一桁の場合には先頭に０をつけて2桁にする。</t>
+    <t>健康保険における被保険者証番号を示す拡張。2桁の半角数字文字列。一桁の場合には先頭に0をつけて2桁にする。</t>
   </si>
   <si>
     <t>Coverage.modifierExtension</t>
@@ -562,37 +562,328 @@
     <t>Business Identifier for the coverage　このカバレッジに割り当てられた一意の識別子【詳細参照】</t>
   </si>
   <si>
-    <t>A unique identifier assigned to this coverage.  
-このカバレッジに割り当てられた一意の識別子。</t>
+    <t>A unique identifier assigned to this coverage.  このカバレッジに割り当てられた一意の識別子。</t>
+  </si>
+  <si>
+    <t>Allows coverages to be distinguished and referenced.  
+カバレッジを区別して参照できるようにする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>IN1-2</t>
+  </si>
+  <si>
+    <t>C.32, C.33, C.39</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子　例）00012345:あいう:１８７:05</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
+  </si>
+  <si>
+    <t>「被保険者個人識別子」の文字列仕様を参照のこと</t>
+  </si>
+  <si>
+    <t>Allows coverages to be distinguished and referenced.</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.system</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/clins/Idsystem/JP_Insurance_memberID</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.value</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
+本仕様では、以下、これを「被保険者個人識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
+被保険者個人識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
+要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者個人識別子」の文字列仕様を参照のこと</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
+  </si>
+  <si>
+    <t>保険者情報を設定</t>
+  </si>
+  <si>
+    <t>保険者情報として[JP_Organization](StructureDefinition-jp-organization.html)を設定する。</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者識別子（CSV形式）　"00012345","１２－３４","５６７８","00"</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報を囲み文字をダブルクォーテーション、区切りをカンマにて連結する</t>
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
 カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
-ルール："{被保険者記号}","{被保険者番号}","{枝番}"  
-例："１２－３４","５６７８","００"</t>
-  </si>
-  <si>
-    <t>Allows coverages to be distinguished and referenced.  
-カバレッジを区別して参照できるようにする。</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>C02</t>
-  </si>
-  <si>
-    <t>IN1-2</t>
-  </si>
-  <si>
-    <t>C.32, C.33, C.39</t>
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/JP_Coverage_id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.value</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。</t>
+  </si>
+  <si>
+    <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
+カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+【JP Core仕様】保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"
+要素を省略する、とある場合には、長さ０の文字列とする。</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>保険者情報</t>
+  </si>
+  <si>
+    <t>健康保険等の保険者情報を設定する。[JP_Organization](StructureDefinition-jp-organization.html)をリソースにて表現する</t>
   </si>
   <si>
     <t>Coverage.status</t>
@@ -613,9 +904,6 @@
 「ドラフト」リソースはさらに編集される可能性があり、「アクティブ」リソースは不変であり、ステータスが「キャンセル」に変更されるだけである可能性があるため、リソースのステータスを追跡する必要がある。</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A code specifying the state of the resource instance.</t>
   </si>
   <si>
@@ -632,10 +920,6 @@
   </si>
   <si>
     <t>Coverage.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Coverage category such as medical or accident　医療保険や事故補償のような分類</t>
@@ -647,7 +931,7 @@
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
 すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。  
-【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”urn:oid:1.2.392.100495.20.2.61”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
+【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
   </si>
   <si>
     <t>The order of application of coverages is dependent on the types of coverage.  
@@ -657,7 +941,7 @@
     <t>The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-type|4.3.0</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -723,10 +1007,6 @@
   </si>
   <si>
     <t>Coverage.subscriberId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>ID assigned to the subscriber　被保険者に割り当てられたID</t>
@@ -740,8 +1020,8 @@
 保険者は、連絡や請求（デジタルおよびその他）でこの識別子を要求する。  
 保険会社は、通信および請求（デジタルおよびその他）でこの識別子を要求する。  
 【JP Core仕様】被保険者記号と番号を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
-ルール："{被保険者記号}","{被保険者番号}"  
-例："１２－３４","５６７８"</t>
+ルール：{被保険者記号}:{被保険者番号}  
+例："あいう","５６７８"</t>
   </si>
   <si>
     <t>Coverage.beneficiary</t>
@@ -788,7 +1068,7 @@
 一部の補償では、単一の識別子が加入者に発行され、次に一意の従属番号が各受益者に発行される。  
 一部の保険では、単一の識別子が加入者に発行され、その後、各受益者に固有の扶養番号が発行される。  
 【JP Core仕様】医療保険で本リソースを使用する場合には、この要素に拡張 InsuredPersonSubNumberに設定した値と同じ、被保険者番号の枝番号全角2桁を設定する。  
-例："００"</t>
+例："00"</t>
   </si>
   <si>
     <t>C17</t>
@@ -813,28 +1093,21 @@
   <si>
     <t>To determine relationship between the patient and the subscriber to determine coordination of benefits.  
 患者と加入者の関係を決定し、給付の調整を決定する。  
-【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される被保険者区分コード（system=”urn:oid:1.2.392.100495.20.2.62”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１２が使用できる。  
+【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される被保険者区分コード（system=”http://jpfhir.jp/fhir/core/mhlw/CodeSystem/InsuredPersonCategory”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１２が使用できる。  
 　1 被保険者  
 　2 被扶養者</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship|4.3.0</t>
   </si>
   <si>
     <t>C03</t>
   </si>
   <si>
     <t>Coverage.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Coverage start and end dates</t>
@@ -845,7 +1118,7 @@
   </si>
   <si>
     <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration).  
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).  
 Period（期間）は時間の範囲を指定する。使用状況は、範囲全体が適用されるか（たとえば、「患者はこの時間範囲で入院していた」）、範囲から1つの値が適用されるか（たとえば、「この2回の間に患者に投与する」）を指定する。  
 Period（期間）は、Duration（時間区間＝経過時間の測定値）には使用されない。 [Duration]（datatypes.html＃Duration）を参照のこと。  
 This is not a duration - that's a measure of time (a separate type), but a duration that occurs at a fixed value of time. A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times"). If duration is required, specify the type as Interval|Duration.  
@@ -877,7 +1150,7 @@
 </t>
   </si>
   <si>
-    <t>Issuer of the policy</t>
+    <t>支払者に関する情報</t>
   </si>
   <si>
     <t>The program or plan underwriter or payor including both insurance and non-insurance agreements, such as patient-pay agreements.  
@@ -935,28 +1208,7 @@
     <t>Coverage.class.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Coverage.class.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Coverage.class.modifierExtension</t>
@@ -997,7 +1249,7 @@
     <t>The policy classifications, eg. Group, Plan, Class, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-class</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-class|4.3.0</t>
   </si>
   <si>
     <t>Coverage.class.value</t>
@@ -1134,16 +1386,13 @@
     <t>The types of services to which patient copayments are specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type|4.3.0</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.id</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.coding</t>
@@ -1328,7 +1577,7 @@
     <t>Coverage.costToBeneficiary.value[x]</t>
   </si>
   <si>
-    <t>Quantity {SimpleQuantity}
+    <t>Quantity {SimpleQuantity|4.3.0}
 Money</t>
   </si>
   <si>
@@ -1386,7 +1635,7 @@
     <t>The types of exceptions from the part or full value of financial obligations such as copays.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception|4.3.0</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.exception.period</t>
@@ -1424,7 +1673,7 @@
     <t>Coverage.contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Contract)
+    <t xml:space="preserve">Reference(Contract|4.3.0)
 </t>
   </si>
   <si>
@@ -1747,20 +1996,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP58"/>
+  <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="21.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="128.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="110.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1769,28 +2018,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="144.8984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.84375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="124.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.83203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.69140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.53125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="59.44921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="51.2734375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="62.85546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="50.96484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="43.95703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="53.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3400,10 +3649,10 @@
         <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3440,16 +3689,14 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>171</v>
@@ -3490,15 +3737,17 @@
         <v>183</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>91</v>
@@ -3507,25 +3756,25 @@
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3550,13 +3799,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3574,13 +3823,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3589,30 +3838,30 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3632,23 +3881,19 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>195</v>
+        <v>93</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3672,13 +3917,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3696,34 +3941,34 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AG16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM16" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3731,21 +3976,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3754,23 +3999,21 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3806,57 +4049,57 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>212</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>213</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3873,25 +4116,25 @@
         <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3916,13 +4159,11 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3940,7 +4181,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3958,27 +4199,27 @@
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>213</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4001,17 +4242,19 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4036,13 +4279,11 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -4078,27 +4319,27 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>213</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4121,32 +4362,32 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>80</v>
@@ -4182,10 +4423,10 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>91</v>
@@ -4197,30 +4438,30 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>213</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4228,7 +4469,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4243,20 +4484,18 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4268,7 +4507,7 @@
         <v>80</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>80</v>
@@ -4304,7 +4543,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4322,16 +4561,16 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4339,10 +4578,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4362,23 +4601,19 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4402,13 +4637,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4426,7 +4661,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4444,16 +4679,16 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4461,10 +4696,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4487,20 +4722,18 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4548,7 +4781,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4563,13 +4796,13 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4586,18 +4819,20 @@
         <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4609,7 +4844,7 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>260</v>
@@ -4621,7 +4856,7 @@
         <v>262</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>263</v>
+        <v>188</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4670,10 +4905,10 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>171</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>82</v>
@@ -4685,30 +4920,30 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>264</v>
+        <v>179</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>266</v>
+        <v>181</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>267</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4719,7 +4954,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -4731,20 +4966,16 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>269</v>
+        <v>93</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4792,25 +5023,25 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>193</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4827,21 +5058,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>275</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4853,15 +5084,17 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>221</v>
+        <v>137</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>197</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4898,37 +5131,37 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>200</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>279</v>
+        <v>194</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -4945,44 +5178,46 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>203</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>204</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -5006,13 +5241,11 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5030,25 +5263,25 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>209</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>279</v>
+        <v>210</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -5057,7 +5290,7 @@
         <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5065,45 +5298,45 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5128,13 +5361,11 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -5152,25 +5383,25 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
@@ -5179,7 +5410,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5187,10 +5418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5213,32 +5444,32 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>292</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>80</v>
@@ -5250,13 +5481,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>295</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -5274,10 +5505,10 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>91</v>
@@ -5292,7 +5523,7 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
@@ -5301,7 +5532,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>80</v>
+        <v>232</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5309,10 +5540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5335,20 +5566,18 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5360,7 +5589,7 @@
         <v>80</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>80</v>
@@ -5396,10 +5625,10 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>91</v>
@@ -5414,27 +5643,27 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>302</v>
+        <v>241</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5457,18 +5686,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>245</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>307</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5516,7 +5743,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5534,27 +5761,27 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5577,20 +5804,18 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>309</v>
+        <v>252</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5638,7 +5863,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5656,7 +5881,7 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
@@ -5665,7 +5890,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5673,10 +5898,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5684,7 +5909,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>91</v>
@@ -5693,23 +5918,25 @@
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>317</v>
+        <v>280</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5734,13 +5961,13 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5758,10 +5985,10 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>314</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>91</v>
@@ -5773,16 +6000,16 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -5793,21 +6020,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5816,22 +6043,22 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5856,13 +6083,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -5880,19 +6107,19 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>274</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5901,13 +6128,13 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5915,10 +6142,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5938,19 +6165,23 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>221</v>
+        <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5998,7 +6229,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6010,44 +6241,44 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6056,21 +6287,23 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6118,80 +6351,78 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>169</v>
+        <v>314</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6240,45 +6471,45 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6286,7 +6517,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>91</v>
@@ -6301,19 +6532,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>195</v>
+        <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6338,13 +6569,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6362,10 +6593,10 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>91</v>
@@ -6377,30 +6608,30 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>321</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6420,19 +6651,23 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6480,7 +6715,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6492,22 +6727,22 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6515,21 +6750,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6541,18 +6776,20 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>281</v>
+        <v>330</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>282</v>
+        <v>331</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6576,55 +6813,55 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6635,10 +6872,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6649,7 +6886,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6661,19 +6898,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6722,13 +6959,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -6737,19 +6974,19 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6757,10 +6994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6768,10 +7005,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6780,19 +7017,23 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>93</v>
+        <v>347</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6840,49 +7081,49 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>80</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6901,18 +7142,20 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>357</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>281</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>282</v>
+        <v>359</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6948,19 +7191,19 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>283</v>
+        <v>356</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6972,13 +7215,13 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>362</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6995,10 +7238,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7018,23 +7261,19 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>235</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>191</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7082,7 +7321,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>193</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7094,13 +7333,13 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>355</v>
+        <v>194</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7109,7 +7348,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7117,21 +7356,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7140,19 +7379,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>221</v>
+        <v>137</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>358</v>
+        <v>197</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>359</v>
+        <v>198</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>360</v>
+        <v>168</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7202,25 +7441,25 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>362</v>
+        <v>194</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7229,7 +7468,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>363</v>
+        <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7237,45 +7476,45 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>366</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>367</v>
+        <v>168</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>368</v>
+        <v>169</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7330,19 +7569,19 @@
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7351,7 +7590,7 @@
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7359,10 +7598,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7370,7 +7609,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>91</v>
@@ -7385,17 +7624,19 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7420,13 +7661,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>376</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7444,10 +7685,10 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>91</v>
@@ -7462,7 +7703,7 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>377</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7471,7 +7712,7 @@
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7479,10 +7720,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7490,7 +7731,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -7505,19 +7746,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7566,10 +7807,10 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>91</v>
@@ -7584,27 +7825,27 @@
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>80</v>
+        <v>384</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7627,19 +7868,17 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7688,7 +7927,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7706,27 +7945,27 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>394</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>80</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7734,7 +7973,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>91</v>
@@ -7749,19 +7988,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7810,10 +8049,10 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>91</v>
@@ -7834,21 +8073,21 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7859,7 +8098,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7868,20 +8107,20 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7930,19 +8169,19 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>274</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -7954,7 +8193,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>80</v>
+        <v>399</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -7965,21 +8204,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7991,16 +8230,20 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>221</v>
+        <v>357</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>276</v>
+        <v>402</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8048,25 +8291,25 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>278</v>
+        <v>400</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -8090,14 +8333,14 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8109,17 +8352,15 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8168,25 +8409,25 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>283</v>
+        <v>193</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>279</v>
+        <v>194</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8210,7 +8451,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>285</v>
+        <v>165</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8223,26 +8464,24 @@
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>286</v>
+        <v>197</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>287</v>
+        <v>198</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8290,7 +8529,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>288</v>
+        <v>200</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8308,7 +8547,7 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8332,36 +8571,38 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>366</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>409</v>
+        <v>367</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>411</v>
+        <v>169</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8386,13 +8627,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8410,25 +8651,25 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8445,10 +8686,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8471,17 +8712,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8506,13 +8749,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8530,7 +8773,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8565,10 +8808,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8591,20 +8834,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>380</v>
+        <v>93</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>420</v>
+        <v>191</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8652,7 +8891,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>419</v>
+        <v>193</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8664,13 +8903,13 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -8687,14 +8926,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8713,20 +8952,18 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>425</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>426</v>
+        <v>197</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>427</v>
+        <v>198</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8762,19 +8999,19 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>200</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8786,25 +9023,2199 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AO58" t="s" s="2">
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AP58" t="s" s="2">
+      <c r="M62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K73" t="s" s="2">
         <v>213</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
@@ -1118,7 +1118,7 @@
   </si>
   <si>
     <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).  
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration).  
 Period（期間）は時間の範囲を指定する。使用状況は、範囲全体が適用されるか（たとえば、「患者はこの時間範囲で入院していた」）、範囲から1つの値が適用されるか（たとえば、「この2回の間に患者に投与する」）を指定する。  
 Period（期間）は、Duration（時間区間＝経過時間の測定値）には使用されない。 [Duration]（datatypes.html＃Duration）を参照のこと。  
 This is not a duration - that's a measure of time (a separate type), but a duration that occurs at a fixed value of time. A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times"). If duration is required, specify the type as Interval|Duration.  

--- a/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-coverage.xlsx
@@ -279,8 +279,8 @@
 Coverageには、保険証レベルの情報が含まれている。これは、保険金請求やプロバイダと保険会社間のその他の通信で提供するのが通例である。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -302,13 +302,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -321,16 +321,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -341,13 +341,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -360,19 +360,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -392,13 +392,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -418,19 +418,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -460,8 +460,8 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Coverage.extension:insuredPersonSymbol</t>
@@ -487,8 +487,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Coverage.extension:insuredPersonNumber</t>
@@ -536,17 +536,18 @@
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -606,7 +607,7 @@
     <t>「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
-    <t>Allows coverages to be distinguished and referenced.</t>
+    <t>カバレッジを区別し、参照することができます。 / Allows coverages to be distinguished and referenced.</t>
   </si>
   <si>
     <t>Coverage.identifier:insuranceIdentifier.id</t>
@@ -615,10 +616,10 @@
     <t>Coverage.identifier.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -633,10 +634,10 @@
     <t>Coverage.identifier.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -651,16 +652,16 @@
     <t>Coverage.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
@@ -685,16 +686,16 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -715,16 +716,16 @@
     <t>Coverage.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/clins/Idsystem/JP_Insurance_memberID</t>
@@ -758,7 +759,7 @@
 要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -783,10 +784,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -889,7 +890,7 @@
     <t>Coverage.status</t>
   </si>
   <si>
-    <t>active | cancelled | draft | entered-in-error</t>
+    <t>アクティブ|キャンセル|ドラフト|エラー入力 / active | cancelled | draft | entered-in-error</t>
   </si>
   <si>
     <t>The status of the resource instance.  
@@ -904,7 +905,7 @@
 「ドラフト」リソースはさらに編集される可能性があり、「アクティブ」リソースは不変であり、ステータスが「キャンセル」に変更されるだけである可能性があるため、リソースのステータスを追跡する必要がある。</t>
   </si>
   <si>
-    <t>A code specifying the state of the resource instance.</t>
+    <t>リソースインスタンスの状態を指定するコード。 / A code specifying the state of the resource instance.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/fm-status|4.3.0</t>
@@ -938,7 +939,7 @@
 カバレッジの適用順序は、カバレッジのタイプによって異なる。</t>
   </si>
   <si>
-    <t>The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
+    <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/coverage-type|4.3.0</t>
@@ -1031,7 +1032,7 @@
 </t>
   </si>
   <si>
-    <t>Plan beneficiary</t>
+    <t>受益者を計画します / Plan beneficiary</t>
   </si>
   <si>
     <t>The party who benefits from the insurance coverage; the patient when products and/or services are provided.  
@@ -1098,7 +1099,7 @@
 　2 被扶養者</t>
   </si>
   <si>
-    <t>The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
+    <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/subscriber-relationship|4.3.0</t>
@@ -1110,7 +1111,7 @@
     <t>Coverage.period</t>
   </si>
   <si>
-    <t>Coverage start and end dates</t>
+    <t>カバレッジの開始日と終了日 / Coverage start and end dates</t>
   </si>
   <si>
     <t>Time period during which the coverage is in force. A missing start date indicates the start date isn't known, a missing end date means the coverage is continuing to be in force.  
@@ -1186,7 +1187,7 @@
 </t>
   </si>
   <si>
-    <t>Additional coverage classifications</t>
+    <t>追加のカバレッジ分類 / Additional coverage classifications</t>
   </si>
   <si>
     <t>A suite of underwriter specific classifiers.  
@@ -1201,7 +1202,7 @@
 健康カードに記載されているコードで、保険者の特定の保険契約を識別または確認するもの。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1218,10 +1219,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1231,7 +1233,7 @@
     <t>Coverage.class.type</t>
   </si>
   <si>
-    <t>Type of class such as 'group' or 'plan'</t>
+    <t>「グループ」や「計画」などのクラスのタイプ / Type of class such as 'group' or 'plan'</t>
   </si>
   <si>
     <t>The type of classification for which an insurer-specific class label or number and optional name is provided, for example may be used to identify a class of coverage or employer group, Policy, Plan.  
@@ -1246,7 +1248,7 @@
 保険者が発行した特定の健康カード番号のラベル。</t>
   </si>
   <si>
-    <t>The policy classifications, eg. Group, Plan, Class, etc.</t>
+    <t>ポリシー分類、例。グループ、プラン、クラスなど / The policy classifications, eg. Group, Plan, Class, etc.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/coverage-class|4.3.0</t>
@@ -1255,7 +1257,7 @@
     <t>Coverage.class.value</t>
   </si>
   <si>
-    <t>Value associated with the type</t>
+    <t>タイプに関連付けられた値 / Value associated with the type</t>
   </si>
   <si>
     <t>The alphanumeric string value associated with the insurer issued label.  
@@ -1282,7 +1284,7 @@
     <t>Coverage.class.name</t>
   </si>
   <si>
-    <t>Human readable description of the type and value</t>
+    <t>タイプと価値の人間の読み取り可能な説明 / Human readable description of the type and value</t>
   </si>
   <si>
     <t>A short description for the class.  
@@ -1300,7 +1302,7 @@
 </t>
   </si>
   <si>
-    <t>Relative order of the coverage</t>
+    <t>カバレッジの相対順序 / Relative order of the coverage</t>
   </si>
   <si>
     <t>The order of applicability of this coverage relative to other coverages which are currently in force. Note, there may be gaps in the numbering and this does not imply primary, secondary etc. as the specific positioning of coverages depends upon the episode of care.  
@@ -1319,7 +1321,7 @@
     <t>Coverage.network</t>
   </si>
   <si>
-    <t>Insurer network</t>
+    <t>保険会社ネットワーク / Insurer network</t>
   </si>
   <si>
     <t>The insurer-specific identifier for the insurer-defined network of providers to which the beneficiary may seek treatment which will be covered at the 'in-network' rate, otherwise 'out of network' terms and conditions apply.  
@@ -1368,7 +1370,7 @@
     <t>Coverage.costToBeneficiary.type</t>
   </si>
   <si>
-    <t>Cost category</t>
+    <t>コストカテゴリ / Cost category</t>
   </si>
   <si>
     <t>The category of patient centric costs associated with treatment.  
@@ -1383,7 +1385,7 @@
 患者の金額に関連するカテゴリーを特定する必要があった。</t>
   </si>
   <si>
-    <t>The types of services to which patient copayments are specified.</t>
+    <t>患者の自己負担が指定されているサービスの種類。 / The types of services to which patient copayments are specified.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/coverage-copay-type|4.3.0</t>
@@ -1402,16 +1404,16 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1432,10 +1434,10 @@
     <t>Coverage.costToBeneficiary.type.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
   </si>
   <si>
     <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.  
@@ -1443,7 +1445,7 @@
 "http://terminology.hl7.org/CodeSystem/coverage-copay-type"</t>
   </si>
   <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1458,13 +1460,13 @@
     <t>Coverage.costToBeneficiary.type.coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
   </si>
   <si>
     <t>Coding.version</t>
@@ -1479,17 +1481,17 @@
     <t>Coverage.costToBeneficiary.type.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
     <t>Note that FHIR strings SHALL NOT exceed 1MB in size  
 自己負担率を表すコード　"copaypct"</t>
   </si>
   <si>
-    <t>Need to refer to a particular code in the system.</t>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1504,13 +1506,13 @@
     <t>Coverage.costToBeneficiary.type.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -1529,16 +1531,16 @@
 </t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
   </si>
   <si>
     <t>Coding.userSelected</t>
@@ -1553,16 +1555,16 @@
     <t>Coverage.costToBeneficiary.type.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -1581,7 +1583,7 @@
 Money</t>
   </si>
   <si>
-    <t>The amount or percentage due from the beneficiary</t>
+    <t>受益者からの金額または割合 / The amount or percentage due from the beneficiary</t>
   </si>
   <si>
     <t>The amount due from the patient for the cost category.  
@@ -1599,7 +1601,7 @@
     <t>Coverage.costToBeneficiary.exception</t>
   </si>
   <si>
-    <t>Exceptions for patient payments</t>
+    <t>患者の支払いの例外 / Exceptions for patient payments</t>
   </si>
   <si>
     <t>A suite of codes indicating exceptions or reductions to patient costs and their effective periods.  
@@ -1618,7 +1620,7 @@
     <t>Coverage.costToBeneficiary.exception.type</t>
   </si>
   <si>
-    <t>Exception category</t>
+    <t>例外カテゴリ / Exception category</t>
   </si>
   <si>
     <t>The code for the specific exception.  
@@ -1632,7 +1634,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>The types of exceptions from the part or full value of financial obligations such as copays.</t>
+    <t>部品からの例外の種類またはCopaysなどの財務義務の完全な価値。 / The types of exceptions from the part or full value of financial obligations such as copays.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception|4.3.0</t>
@@ -1641,7 +1643,7 @@
     <t>Coverage.costToBeneficiary.exception.period</t>
   </si>
   <si>
-    <t>The effective period of the exception</t>
+    <t>例外の有効期間 / The effective period of the exception</t>
   </si>
   <si>
     <t>The timeframe during when the exception is in force.  
@@ -2023,7 +2025,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="124.2265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="49.83203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
